--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487852_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487852_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.2132</v>
+        <v>6.4671</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3217</v>
+        <v>5.4288</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8915</v>
+        <v>1.0383</v>
       </c>
       <c r="G2" t="n">
         <v>5.0652</v>
@@ -610,13 +610,13 @@
         <v>1.8731</v>
       </c>
       <c r="S2" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.3394</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.46</v>
+        <v>-0.3528</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5455</v>
+        <v>0.6923</v>
       </c>
       <c r="V2" t="n">
         <v>0.23</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. NDIAYE</t>
+          <t>A. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7675</v>
+        <v>2.703</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2146</v>
+        <v>0.6856</v>
       </c>
       <c r="F3" t="n">
-        <v>0.553</v>
+        <v>2.0174</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.8015</v>
+        <v>-0.7984</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.3581</v>
+        <v>-1.2924</v>
       </c>
       <c r="I3" t="n">
-        <v>-1.4434</v>
+        <v>0.4939</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4358</v>
+        <v>-0.6227</v>
       </c>
       <c r="K3" t="n">
-        <v>0.279</v>
+        <v>-0.9003</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1568</v>
+        <v>0.2776</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2373</v>
+        <v>-0.1757</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6371</v>
+        <v>-0.3921</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.6002</v>
+        <v>0.2164</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.2081</v>
+        <v>0.8325</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.0812</v>
+        <v>-1.0406</v>
       </c>
       <c r="R3" t="n">
         <v>1.8731</v>
       </c>
       <c r="S3" t="n">
-        <v>3.0259</v>
+        <v>0.5639</v>
       </c>
       <c r="T3" t="n">
-        <v>1.295</v>
+        <v>0.0138</v>
       </c>
       <c r="U3" t="n">
-        <v>1.7309</v>
+        <v>0.55</v>
       </c>
       <c r="V3" t="n">
-        <v>1.7513</v>
+        <v>2.1051</v>
       </c>
       <c r="W3" t="n">
-        <v>2.565</v>
+        <v>2.3351</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.8137</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. OROZCO DOMINGUEZ</t>
+          <t>G. OROZCO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1672</v>
+        <v>2.0009</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1498</v>
+        <v>1.1756</v>
       </c>
       <c r="F4" t="n">
-        <v>2.0174</v>
+        <v>0.8253</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.7984</v>
+        <v>1.2145</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2924</v>
+        <v>0.1107</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4939</v>
+        <v>1.1038</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.6227</v>
+        <v>1.7291</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9003</v>
+        <v>0.9846</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2776</v>
+        <v>0.7446</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1757</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3921</v>
+        <v>-0.8738</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2164</v>
+        <v>0.3592</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8325</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.0406</v>
+        <v>-2.0812</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8731</v>
+        <v>1.6649</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0281</v>
+        <v>0.8488</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.5219</v>
+        <v>0.3601</v>
       </c>
       <c r="U4" t="n">
-        <v>0.55</v>
+        <v>0.4887</v>
       </c>
       <c r="V4" t="n">
-        <v>2.1051</v>
+        <v>0.3538</v>
       </c>
       <c r="W4" t="n">
-        <v>2.3351</v>
+        <v>1.1675</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.23</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.847</v>
+        <v>1.9747</v>
       </c>
       <c r="E5" t="n">
-        <v>0.8955</v>
+        <v>0.7883</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9515</v>
+        <v>1.1864</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4772</v>
@@ -844,13 +844,13 @@
         <v>1.6649</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5324</v>
+        <v>0.6601</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1924</v>
+        <v>0.0853</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3399</v>
+        <v>0.5748</v>
       </c>
       <c r="V5" t="n">
         <v>1.1675</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. SCHUTTE</t>
+          <t>S. NDIAYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.7884</v>
+        <v>1.4493</v>
       </c>
       <c r="E6" t="n">
-        <v>2.5915</v>
+        <v>1.5716</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8031</v>
+        <v>-0.1223</v>
       </c>
       <c r="G6" t="n">
-        <v>1.0754</v>
+        <v>-1.8015</v>
       </c>
       <c r="H6" t="n">
-        <v>0.6075</v>
+        <v>-0.3581</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4678</v>
+        <v>-1.4434</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1285</v>
+        <v>0.4358</v>
       </c>
       <c r="K6" t="n">
-        <v>1.0893</v>
+        <v>0.279</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0392</v>
+        <v>0.1568</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0532</v>
+        <v>-2.2373</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.4818</v>
+        <v>-0.6371</v>
       </c>
       <c r="O6" t="n">
-        <v>0.4286</v>
+        <v>-1.6002</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4162</v>
+        <v>-0.2081</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0812</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4162</v>
+        <v>1.8731</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2343</v>
+        <v>1.7077</v>
       </c>
       <c r="T6" t="n">
-        <v>1.233</v>
+        <v>0.652</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0013</v>
+        <v>1.0557</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.9376</v>
+        <v>1.7513</v>
       </c>
       <c r="W6" t="n">
-        <v>0.23</v>
+        <v>2.565</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.1675</v>
+        <v>-0.8137</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. OROZCO DOMINGUEZ</t>
+          <t>K. SCHUTTE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.719</v>
+        <v>0.9795</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7469</v>
+        <v>1.8414</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9721</v>
+        <v>-0.8618</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2145</v>
+        <v>1.0754</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1107</v>
+        <v>0.6075</v>
       </c>
       <c r="I7" t="n">
-        <v>1.1038</v>
+        <v>0.4678</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7291</v>
+        <v>1.1285</v>
       </c>
       <c r="K7" t="n">
-        <v>0.9846</v>
+        <v>1.0893</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7446</v>
+        <v>0.0392</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.5145999999999999</v>
+        <v>-0.0532</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.8738</v>
+        <v>-0.4818</v>
       </c>
       <c r="O7" t="n">
-        <v>0.3592</v>
+        <v>0.4286</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.0812</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.6649</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5669999999999999</v>
+        <v>0.4255</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.4829</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6355</v>
+        <v>-0.0574</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3538</v>
+        <v>-0.9376</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1675</v>
+        <v>0.23</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8137</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.7921</v>
+        <v>-0.3253</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5012</v>
+        <v>0.1417</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2909</v>
+        <v>-0.467</v>
       </c>
       <c r="G8" t="n">
         <v>-1.9733</v>
@@ -1078,13 +1078,13 @@
         <v>1.0406</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.08939999999999999</v>
+        <v>0.3774</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8482</v>
+        <v>-0.2052</v>
       </c>
       <c r="U8" t="n">
-        <v>0.7588</v>
+        <v>0.5826</v>
       </c>
       <c r="V8" t="n">
         <v>0.23</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. SIENCHE GUEMETA</t>
+          <t>F. BELLO MOURE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.884</v>
+        <v>-1.2469</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.7187</v>
+        <v>-1.4701</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1653</v>
+        <v>0.2232</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5331</v>
+        <v>-1.5855</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5225</v>
+        <v>-1.1749</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0556</v>
+        <v>-0.4107</v>
       </c>
       <c r="J9" t="n">
-        <v>1.1081</v>
+        <v>-0.3362</v>
       </c>
       <c r="K9" t="n">
-        <v>1.2044</v>
+        <v>-0.4929</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0963</v>
+        <v>0.1568</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.6412</v>
+        <v>-1.2494</v>
       </c>
       <c r="N9" t="n">
         <v>-0.6820000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.9593</v>
+        <v>-0.5674</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8731</v>
+        <v>1.0406</v>
       </c>
       <c r="S9" t="n">
-        <v>1.9415</v>
+        <v>-0.139</v>
       </c>
       <c r="T9" t="n">
-        <v>1.295</v>
+        <v>-0.09329999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6466</v>
+        <v>-0.0456</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.0437</v>
+        <v>0.4776</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0437</v>
+        <v>0.4776</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. BELLO MOURE</t>
+          <t>J. SIENCHE GUEMETA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.881</v>
+        <v>-1.5357</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8987</v>
+        <v>-1.576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.0177</v>
+        <v>0.0402</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.5855</v>
+        <v>-0.5331</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1749</v>
+        <v>0.5225</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.4107</v>
+        <v>-1.0556</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3362</v>
+        <v>1.1081</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.4929</v>
+        <v>1.2044</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1568</v>
+        <v>-0.0963</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2494</v>
+        <v>-1.6412</v>
       </c>
       <c r="N10" t="n">
         <v>-0.6820000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.5674</v>
+        <v>-0.9593</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.0406</v>
+        <v>-3.1218</v>
       </c>
       <c r="R10" t="n">
-        <v>1.0406</v>
+        <v>1.8731</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7731</v>
+        <v>1.2898</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5219</v>
+        <v>0.4377</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2511</v>
+        <v>0.8521</v>
       </c>
       <c r="V10" t="n">
-        <v>0.4776</v>
+        <v>-1.0437</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4776</v>
+        <v>-1.0437</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.8458</v>
+        <v>-2.3673</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7352</v>
+        <v>-1.5209</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1107</v>
+        <v>-0.8464</v>
       </c>
       <c r="G11" t="n">
         <v>-1.186</v>
@@ -1312,13 +1312,13 @@
         <v>1.2487</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3706</v>
+        <v>0.108</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.3729</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2166</v>
+        <v>0.4809</v>
       </c>
       <c r="V11" t="n">
         <v>0.5838</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>10.0994</v>
+        <v>10.0993</v>
       </c>
       <c r="E12" t="n">
-        <v>7.066199999999999</v>
+        <v>7.066</v>
       </c>
       <c r="F12" t="n">
-        <v>3.033199999999999</v>
+        <v>3.033299999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9999000000000002</v>
+        <v>-0.999900000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>0.9592999999999998</v>
+        <v>0.9592999999999994</v>
       </c>
       <c r="I12" t="n">
         <v>-1.9594</v>
@@ -1366,7 +1366,7 @@
         <v>11.5343</v>
       </c>
       <c r="K12" t="n">
-        <v>5.8602</v>
+        <v>5.860199999999999</v>
       </c>
       <c r="L12" t="n">
         <v>5.674199999999999</v>
@@ -1393,13 +1393,13 @@
         <v>6.1816</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0077</v>
+        <v>1.0076</v>
       </c>
       <c r="U12" t="n">
-        <v>5.173999999999999</v>
+        <v>5.1741</v>
       </c>
       <c r="V12" t="n">
-        <v>4.9178</v>
+        <v>4.917800000000001</v>
       </c>
       <c r="W12" t="n">
         <v>9.092600000000001</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.3145</v>
+        <v>4.3684</v>
       </c>
       <c r="E13" t="n">
-        <v>2.6386</v>
+        <v>3.2815</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6758999999999999</v>
+        <v>1.0869</v>
       </c>
       <c r="G13" t="n">
         <v>2.9539</v>
@@ -1468,13 +1468,13 @@
         <v>1.8731</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.0962</v>
+        <v>-1.0422</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.3701</v>
+        <v>-0.7272</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.7261</v>
+        <v>-0.3151</v>
       </c>
       <c r="V13" t="n">
         <v>0.5838</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7893</v>
+        <v>1.4488</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7237</v>
+        <v>2.295</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.9344</v>
+        <v>-0.8463000000000001</v>
       </c>
       <c r="G14" t="n">
         <v>1.2183</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.8671</v>
+        <v>-1.2076</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3948</v>
+        <v>-0.8234</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4723</v>
+        <v>-0.3842</v>
       </c>
       <c r="V14" t="n">
         <v>0.8137</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2924</v>
+        <v>0.7401</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0716</v>
+        <v>0.4642</v>
       </c>
       <c r="F15" t="n">
-        <v>0.364</v>
+        <v>0.2759</v>
       </c>
       <c r="G15" t="n">
         <v>2.5964</v>
@@ -1624,13 +1624,13 @@
         <v>1.6649</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.7202</v>
+        <v>-0.2725</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.7829</v>
+        <v>-0.2471</v>
       </c>
       <c r="U15" t="n">
-        <v>0.06270000000000001</v>
+        <v>-0.0254</v>
       </c>
       <c r="V15" t="n">
         <v>-1.1675</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.9039</v>
+        <v>-0.7571</v>
       </c>
       <c r="E16" t="n">
         <v>-0.4379</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.466</v>
+        <v>-0.3192</v>
       </c>
       <c r="G16" t="n">
         <v>1.3528</v>
@@ -1702,13 +1702,13 @@
         <v>1.2487</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3836</v>
+        <v>-0.2368</v>
       </c>
       <c r="T16" t="n">
         <v>-0.1957</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.1879</v>
+        <v>-0.0411</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. MCKAY JR</t>
+          <t>M. DENG</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.445</v>
+        <v>-1.4179</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.9234</v>
+        <v>0.4778</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4784</v>
+        <v>-1.8957</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.8117</v>
+        <v>-1.0323</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9104</v>
+        <v>-0.9228</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.9013</v>
+        <v>-0.1094</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5256</v>
+        <v>1.1398</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.0856</v>
+        <v>0.5756</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4401</v>
+        <v>0.5641</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.2861</v>
+        <v>-2.172</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8248</v>
+        <v>-1.4985</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4613</v>
+        <v>-0.6735</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4162</v>
+        <v>1.6649</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4568</v>
+        <v>1.6649</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0496</v>
+        <v>-0.8831</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.6619</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5376</v>
+        <v>-0.2211</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-1.1675</v>
       </c>
       <c r="W17" t="n">
-        <v>0.23</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.23</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6832</v>
+        <v>-1.6245</v>
       </c>
       <c r="E18" t="n">
         <v>-1.0406</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.5839</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1104</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5728</v>
+        <v>-0.5141</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3262</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2466</v>
+        <v>-0.1879</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R. LLAMAS MARTINEZ</t>
+          <t>G. MCKAY JR</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9107</v>
+        <v>-1.7386</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.137</v>
+        <v>-1.9234</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2262</v>
+        <v>0.1848</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4694</v>
+        <v>-1.8117</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1004</v>
+        <v>-0.9104</v>
       </c>
       <c r="I19" t="n">
-        <v>0.369</v>
+        <v>-0.9013</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0941</v>
+        <v>-0.5256</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0148</v>
+        <v>-0.0856</v>
       </c>
       <c r="L19" t="n">
-        <v>1.0793</v>
+        <v>-0.4401</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.6247</v>
+        <v>-1.2861</v>
       </c>
       <c r="N19" t="n">
-        <v>0.0856</v>
+        <v>-0.8248</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7103</v>
+        <v>-0.4613</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.4974</v>
+        <v>0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.1624</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6649</v>
+        <v>1.4568</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.4664</v>
+        <v>-0.3431</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6524</v>
+        <v>-0.5872000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.186</v>
+        <v>0.244</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5838</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. DENG</t>
+          <t>R. LLAMAS MARTINEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4425</v>
+        <v>-2.0282</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1651</v>
+        <v>-3.137</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.2774</v>
+        <v>1.1088</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.0323</v>
+        <v>0.4694</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9228</v>
+        <v>0.1004</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1094</v>
+        <v>0.369</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1398</v>
+        <v>1.0941</v>
       </c>
       <c r="K20" t="n">
-        <v>0.5756</v>
+        <v>0.0148</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5641</v>
+        <v>1.0793</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.172</v>
+        <v>-0.6247</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4985</v>
+        <v>0.0856</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.6735</v>
+        <v>-0.7103</v>
       </c>
       <c r="P20" t="n">
-        <v>1.6649</v>
+        <v>-2.4974</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.1624</v>
       </c>
       <c r="R20" t="n">
         <v>1.6649</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.9077</v>
+        <v>-0.5839</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.3049</v>
+        <v>-0.6524</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6028</v>
+        <v>0.06850000000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.1675</v>
+        <v>0.5838</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.196</v>
+        <v>-4.0944</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6346000000000001</v>
+        <v>-1.0633</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5614</v>
+        <v>-3.0311</v>
       </c>
       <c r="G21" t="n">
         <v>-1.8938</v>
@@ -2092,13 +2092,13 @@
         <v>1.4568</v>
       </c>
       <c r="S21" t="n">
-        <v>0.6374</v>
+        <v>-0.261</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0066</v>
+        <v>-0.4352</v>
       </c>
       <c r="U21" t="n">
-        <v>0.644</v>
+        <v>0.1743</v>
       </c>
       <c r="V21" t="n">
         <v>-3.3965</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.9142</v>
+        <v>-4.996</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.9854000000000001</v>
+        <v>-1.9498</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.9288</v>
+        <v>-3.0462</v>
       </c>
       <c r="G22" t="n">
         <v>-1.7426</v>
@@ -2170,13 +2170,13 @@
         <v>1.8731</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2446</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4468</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2022</v>
+        <v>-0.3196</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1675</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-10.0993</v>
+        <v>-10.0994</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.033300000000001</v>
+        <v>-3.0335</v>
       </c>
       <c r="F23" t="n">
-        <v>-7.0661</v>
+        <v>-7.066</v>
       </c>
       <c r="G23" t="n">
         <v>1.000000000000001</v>
@@ -2248,10 +2248,10 @@
         <v>14.5681</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.1816</v>
+        <v>-6.181500000000001</v>
       </c>
       <c r="T23" t="n">
-        <v>-5.174</v>
+        <v>-5.1739</v>
       </c>
       <c r="U23" t="n">
         <v>-1.0076</v>
